--- a/config/yunying/gateaward.xlsx
+++ b/config/yunying/gateaward.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gateaward" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gateaward" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>第1章ハードモードをクリア</t>
+          <t>第1章清除困难模式</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>第3章ハードモードをクリア</t>
+          <t>第3章清除困难模式</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>第5章ハードモードをクリア</t>
+          <t>第5章清除困难模式</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>第7章ハードモードをクリア</t>
+          <t>第7章清除困难模式</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
